--- a/artfynd/A 22838-2025 artfynd.xlsx
+++ b/artfynd/A 22838-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132719538</v>
       </c>
       <c r="B2" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>132709091</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>132719508</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>132708973</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,49 +1293,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132719417</v>
+        <v>132708885</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786946</v>
+        <v>786988</v>
       </c>
       <c r="R8" t="n">
-        <v>7198752</v>
+        <v>7198494</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1370,13 +1374,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barksprätt tretå</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132719525</v>
+        <v>132719417</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786931</v>
+        <v>786946</v>
       </c>
       <c r="R9" t="n">
-        <v>7198791</v>
+        <v>7198752</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1497,53 +1505,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132708885</v>
+        <v>132719525</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Boviken, Vb</t>
+          <t>boviken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786988</v>
+        <v>786931</v>
       </c>
       <c r="R10" t="n">
-        <v>7198494</v>
+        <v>7198791</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,17 +1582,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Barksprätt tretå</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>132708993</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132709117</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,38 +1811,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132708853</v>
+        <v>132708955</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1850,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786961</v>
+        <v>786998</v>
       </c>
       <c r="R13" t="n">
-        <v>7198478</v>
+        <v>7198497</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1894,7 +1898,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,42 +1916,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132708955</v>
+        <v>132708853</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>99117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1956,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786998</v>
+        <v>786961</v>
       </c>
       <c r="R14" t="n">
-        <v>7198497</v>
+        <v>7198478</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2000,6 +1999,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>132709076</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132709035</v>
+        <v>132709100</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>787022</v>
+        <v>786858</v>
       </c>
       <c r="R16" t="n">
-        <v>7198664</v>
+        <v>7198547</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132709100</v>
+        <v>132709035</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786858</v>
+        <v>787022</v>
       </c>
       <c r="R17" t="n">
-        <v>7198547</v>
+        <v>7198664</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 22838-2025 artfynd.xlsx
+++ b/artfynd/A 22838-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132719538</v>
       </c>
       <c r="B2" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>132709091</v>
       </c>
       <c r="B4" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>132719508</v>
       </c>
       <c r="B6" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>132708973</v>
       </c>
       <c r="B7" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,53 +1293,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132708885</v>
+        <v>132719417</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Boviken, Vb</t>
+          <t>boviken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786988</v>
+        <v>786946</v>
       </c>
       <c r="R8" t="n">
-        <v>7198494</v>
+        <v>7198752</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,17 +1370,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Barksprätt tretå</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132719417</v>
+        <v>132719525</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1442,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786946</v>
+        <v>786931</v>
       </c>
       <c r="R9" t="n">
-        <v>7198752</v>
+        <v>7198791</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,49 +1497,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132719525</v>
+        <v>132708885</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786931</v>
+        <v>786988</v>
       </c>
       <c r="R10" t="n">
-        <v>7198791</v>
+        <v>7198494</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1582,13 +1578,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barksprätt tretå</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>132708993</v>
       </c>
       <c r="B11" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132709117</v>
       </c>
       <c r="B12" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132708853</v>
+        <v>132709076</v>
       </c>
       <c r="B14" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786961</v>
+        <v>787001</v>
       </c>
       <c r="R14" t="n">
-        <v>7198478</v>
+        <v>7198673</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132709076</v>
+        <v>132708853</v>
       </c>
       <c r="B15" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>787001</v>
+        <v>786961</v>
       </c>
       <c r="R15" t="n">
-        <v>7198673</v>
+        <v>7198478</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132709100</v>
+        <v>132709035</v>
       </c>
       <c r="B16" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>786858</v>
+        <v>787022</v>
       </c>
       <c r="R16" t="n">
-        <v>7198547</v>
+        <v>7198664</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132709035</v>
+        <v>132709100</v>
       </c>
       <c r="B17" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>787022</v>
+        <v>786858</v>
       </c>
       <c r="R17" t="n">
-        <v>7198664</v>
+        <v>7198547</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 22838-2025 artfynd.xlsx
+++ b/artfynd/A 22838-2025 artfynd.xlsx
@@ -1293,49 +1293,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132719417</v>
+        <v>132708885</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786946</v>
+        <v>786988</v>
       </c>
       <c r="R8" t="n">
-        <v>7198752</v>
+        <v>7198494</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1370,13 +1374,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barksprätt tretå</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132719525</v>
+        <v>132719417</v>
       </c>
       <c r="B9" t="n">
         <v>99130</v>
@@ -1434,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786931</v>
+        <v>786946</v>
       </c>
       <c r="R9" t="n">
-        <v>7198791</v>
+        <v>7198752</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1497,53 +1505,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132708885</v>
+        <v>132719525</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Boviken, Vb</t>
+          <t>boviken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786988</v>
+        <v>786931</v>
       </c>
       <c r="R10" t="n">
-        <v>7198494</v>
+        <v>7198791</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,17 +1582,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Barksprätt tretå</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22838-2025 artfynd.xlsx
+++ b/artfynd/A 22838-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132719538</v>
+        <v>102666840</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Fällbäcken, Skellefteå, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786920</v>
+        <v>786854</v>
       </c>
       <c r="R2" t="n">
-        <v>7198747</v>
+        <v>7198408</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,33 +755,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Johanna Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Johanna Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132719461</v>
+        <v>132708916</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -810,20 +806,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787004</v>
+        <v>786978</v>
       </c>
       <c r="R3" t="n">
-        <v>7198798</v>
+        <v>7198495</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,38 +878,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132709091</v>
+        <v>132708955</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>786913</v>
+        <v>786998</v>
       </c>
       <c r="R4" t="n">
-        <v>7198668</v>
+        <v>7198497</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,7 +965,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,14 +983,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132708916</v>
+        <v>132719461</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1017,20 +1016,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Boviken, Vb</t>
+          <t>boviken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>786978</v>
+        <v>787004</v>
       </c>
       <c r="R5" t="n">
-        <v>7198495</v>
+        <v>7198798</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,49 +1088,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132719508</v>
+        <v>132708885</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787026</v>
+        <v>786988</v>
       </c>
       <c r="R6" t="n">
-        <v>7198783</v>
+        <v>7198494</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1166,13 +1169,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Barksprätt tretå</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1191,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132708973</v>
+        <v>132708853</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786992</v>
+        <v>786961</v>
       </c>
       <c r="R7" t="n">
-        <v>7198506</v>
+        <v>7198478</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,42 +1300,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132708885</v>
+        <v>132708973</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1336,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786988</v>
+        <v>786992</v>
       </c>
       <c r="R8" t="n">
-        <v>7198494</v>
+        <v>7198506</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,17 +1377,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Barksprätt tretå</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132719417</v>
+        <v>132708993</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,14 +1437,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786946</v>
+        <v>786947</v>
       </c>
       <c r="R9" t="n">
-        <v>7198752</v>
+        <v>7198557</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132719525</v>
+        <v>132709035</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,14 +1539,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>boviken, Vb</t>
+          <t>Boviken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786931</v>
+        <v>787022</v>
       </c>
       <c r="R10" t="n">
-        <v>7198791</v>
+        <v>7198664</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1607,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132708993</v>
+        <v>132709076</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786947</v>
+        <v>787001</v>
       </c>
       <c r="R11" t="n">
-        <v>7198557</v>
+        <v>7198673</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1709,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132709117</v>
+        <v>132709091</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786850</v>
+        <v>786913</v>
       </c>
       <c r="R12" t="n">
-        <v>7198540</v>
+        <v>7198668</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1811,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132708853</v>
+        <v>132709100</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786961</v>
+        <v>786858</v>
       </c>
       <c r="R13" t="n">
-        <v>7198478</v>
+        <v>7198547</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1913,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132709076</v>
+        <v>132709117</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>787001</v>
+        <v>786850</v>
       </c>
       <c r="R14" t="n">
-        <v>7198673</v>
+        <v>7198540</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2015,42 +2014,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132708955</v>
+        <v>132709136</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2058,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786998</v>
+        <v>786833</v>
       </c>
       <c r="R15" t="n">
-        <v>7198497</v>
+        <v>7198527</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2102,6 +2097,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2120,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132709035</v>
+        <v>132716605</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>787022</v>
+        <v>786896</v>
       </c>
       <c r="R16" t="n">
-        <v>7198664</v>
+        <v>7198804</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132709100</v>
+        <v>132716620</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,14 +2253,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Boviken, Vb</t>
+          <t>boviken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786858</v>
+        <v>786906</v>
       </c>
       <c r="R17" t="n">
-        <v>7198547</v>
+        <v>7198791</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2321,6 +2317,414 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132719417</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>boviken, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>786946</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7198752</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132719508</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>boviken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>787026</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7198783</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132719525</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>boviken, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>786931</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7198791</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132719538</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>boviken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>786920</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7198747</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22838-2025 artfynd.xlsx
+++ b/artfynd/A 22838-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102666840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708955</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132719461</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708853</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708973</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708993</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709035</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709076</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709091</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709117</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709136</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2290,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132716605</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132716620</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132719417</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2521,6 +2611,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132719508</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132719525</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,8 +2825,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132719538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>